--- a/input/12cut_non-mix.xlsx
+++ b/input/12cut_non-mix.xlsx
@@ -1804,6 +1804,36 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1811,30 +1841,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1843,11 +1849,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -1858,11 +1864,38 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
       <alignment horizontal="center" vertical="center"/>
@@ -1909,40 +1942,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="56">
@@ -1954,145 +1969,136 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="56">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
@@ -2101,73 +2107,67 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2665,31 +2665,31 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="312" t="inlineStr">
+      <c r="A2" s="314" t="inlineStr">
         <is>
           <t>NEW AB</t>
         </is>
       </c>
-      <c r="B2" s="312" t="inlineStr">
+      <c r="B2" s="314" t="inlineStr">
         <is>
           <t>mix</t>
         </is>
       </c>
-      <c r="C2" s="312" t="inlineStr">
+      <c r="C2" s="314" t="inlineStr">
         <is>
           <t>1000-1200</t>
         </is>
       </c>
-      <c r="D2" s="312" t="n">
+      <c r="D2" s="314" t="n">
         <v>700</v>
       </c>
-      <c r="E2" s="312" t="n">
+      <c r="E2" s="314" t="n">
         <v>17</v>
       </c>
-      <c r="F2" s="312" t="n">
+      <c r="F2" s="314" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="312">
+      <c r="G2" s="314">
         <f>E2-F2</f>
         <v/>
       </c>
@@ -2703,33 +2703,33 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="301" t="inlineStr">
+      <c r="A3" s="311" t="inlineStr">
         <is>
           <t xml:space="preserve">LT.SIAM </t>
         </is>
       </c>
-      <c r="B3" s="301" t="inlineStr">
+      <c r="B3" s="311" t="inlineStr">
         <is>
           <t>mix</t>
         </is>
       </c>
-      <c r="C3" s="301" t="inlineStr">
+      <c r="C3" s="311" t="inlineStr">
         <is>
           <t>1000-1200</t>
         </is>
       </c>
-      <c r="D3" s="301" t="n">
+      <c r="D3" s="311" t="n">
         <v>300</v>
       </c>
-      <c r="E3" s="301">
+      <c r="E3" s="311">
         <f>14+6</f>
         <v/>
       </c>
-      <c r="F3" s="301">
+      <c r="F3" s="311">
         <f>1+1+1</f>
         <v/>
       </c>
-      <c r="G3" s="301">
+      <c r="G3" s="311">
         <f>E3-F3</f>
         <v/>
       </c>
@@ -2745,32 +2745,32 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="301" t="inlineStr">
+      <c r="A4" s="311" t="inlineStr">
         <is>
           <t>Siam</t>
         </is>
       </c>
-      <c r="B4" s="301" t="inlineStr">
+      <c r="B4" s="311" t="inlineStr">
         <is>
           <t>mix</t>
         </is>
       </c>
-      <c r="C4" s="301" t="inlineStr">
+      <c r="C4" s="311" t="inlineStr">
         <is>
           <t>1000-1200</t>
         </is>
       </c>
-      <c r="D4" s="301" t="n">
+      <c r="D4" s="311" t="n">
         <v>300</v>
       </c>
-      <c r="E4" s="301" t="n">
+      <c r="E4" s="311" t="n">
         <v>7</v>
       </c>
-      <c r="F4" s="301">
+      <c r="F4" s="311">
         <f>1+1</f>
         <v/>
       </c>
-      <c r="G4" s="301">
+      <c r="G4" s="311">
         <f>E4-F4</f>
         <v/>
       </c>
@@ -2786,31 +2786,31 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="301" t="inlineStr">
+      <c r="A5" s="311" t="inlineStr">
         <is>
           <t>Dark Siam</t>
         </is>
       </c>
-      <c r="B5" s="301" t="inlineStr">
+      <c r="B5" s="311" t="inlineStr">
         <is>
           <t>mix</t>
         </is>
       </c>
-      <c r="C5" s="301" t="inlineStr">
+      <c r="C5" s="311" t="inlineStr">
         <is>
           <t>1000-1200</t>
         </is>
       </c>
-      <c r="D5" s="301" t="n">
+      <c r="D5" s="311" t="n">
         <v>300</v>
       </c>
-      <c r="E5" s="301" t="n">
+      <c r="E5" s="311" t="n">
         <v>9</v>
       </c>
-      <c r="F5" s="301" t="n">
+      <c r="F5" s="311" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="301">
+      <c r="G5" s="311">
         <f>E5-F5</f>
         <v/>
       </c>
@@ -2826,32 +2826,32 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="301" t="inlineStr">
+      <c r="A6" s="311" t="inlineStr">
         <is>
           <t>HYACINTH</t>
         </is>
       </c>
-      <c r="B6" s="301" t="inlineStr">
+      <c r="B6" s="311" t="inlineStr">
         <is>
           <t>mix</t>
         </is>
       </c>
-      <c r="C6" s="301" t="inlineStr">
+      <c r="C6" s="311" t="inlineStr">
         <is>
           <t>1000-1200</t>
         </is>
       </c>
-      <c r="D6" s="301" t="n">
+      <c r="D6" s="311" t="n">
         <v>400</v>
       </c>
-      <c r="E6" s="301">
+      <c r="E6" s="311">
         <f>5+7</f>
         <v/>
       </c>
-      <c r="F6" s="301" t="n">
+      <c r="F6" s="311" t="n">
         <v>2</v>
       </c>
-      <c r="G6" s="301">
+      <c r="G6" s="311">
         <f>E6-F6</f>
         <v/>
       </c>
@@ -2867,31 +2867,31 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="301" t="inlineStr">
+      <c r="A7" s="311" t="inlineStr">
         <is>
           <t xml:space="preserve">Sun Shine </t>
         </is>
       </c>
-      <c r="B7" s="301" t="inlineStr">
+      <c r="B7" s="311" t="inlineStr">
         <is>
           <t>mix</t>
         </is>
       </c>
-      <c r="C7" s="301" t="inlineStr">
+      <c r="C7" s="311" t="inlineStr">
         <is>
           <t>1000-1200</t>
         </is>
       </c>
-      <c r="D7" s="301" t="n">
+      <c r="D7" s="311" t="n">
         <v>300</v>
       </c>
-      <c r="E7" s="301" t="n">
+      <c r="E7" s="311" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="301" t="n">
+      <c r="F7" s="311" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="301">
+      <c r="G7" s="311">
         <f>E7-F7</f>
         <v/>
       </c>
@@ -2907,33 +2907,33 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="301" t="inlineStr">
+      <c r="A8" s="311" t="inlineStr">
         <is>
           <t>JET BLACK</t>
         </is>
       </c>
-      <c r="B8" s="301" t="inlineStr">
+      <c r="B8" s="311" t="inlineStr">
         <is>
           <t>mix</t>
         </is>
       </c>
-      <c r="C8" s="301" t="inlineStr">
+      <c r="C8" s="311" t="inlineStr">
         <is>
           <t>1000-1200</t>
         </is>
       </c>
-      <c r="D8" s="301" t="n">
+      <c r="D8" s="311" t="n">
         <v>350</v>
       </c>
-      <c r="E8" s="301">
+      <c r="E8" s="311">
         <f>11+2+9</f>
         <v/>
       </c>
-      <c r="F8" s="301">
+      <c r="F8" s="311">
         <f>1+1</f>
         <v/>
       </c>
-      <c r="G8" s="301">
+      <c r="G8" s="311">
         <f>E8-F8</f>
         <v/>
       </c>
@@ -2949,32 +2949,32 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="301" t="inlineStr">
+      <c r="A9" s="311" t="inlineStr">
         <is>
           <t>GREEN ZIRCON</t>
         </is>
       </c>
-      <c r="B9" s="301" t="inlineStr">
+      <c r="B9" s="311" t="inlineStr">
         <is>
           <t>mix</t>
         </is>
       </c>
-      <c r="C9" s="301" t="inlineStr">
+      <c r="C9" s="311" t="inlineStr">
         <is>
           <t>1000-1200</t>
         </is>
       </c>
-      <c r="D9" s="301" t="n">
+      <c r="D9" s="311" t="n">
         <v>400</v>
       </c>
-      <c r="E9" s="301">
+      <c r="E9" s="311">
         <f>7+1</f>
         <v/>
       </c>
-      <c r="F9" s="301" t="n">
+      <c r="F9" s="311" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="301">
+      <c r="G9" s="311">
         <f>E9-F9</f>
         <v/>
       </c>
@@ -2990,32 +2990,32 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="301" t="inlineStr">
+      <c r="A10" s="311" t="inlineStr">
         <is>
           <t>SAPPHIRE</t>
         </is>
       </c>
-      <c r="B10" s="301" t="inlineStr">
+      <c r="B10" s="311" t="inlineStr">
         <is>
           <t>mix</t>
         </is>
       </c>
-      <c r="C10" s="301" t="inlineStr">
+      <c r="C10" s="311" t="inlineStr">
         <is>
           <t>1000-1200</t>
         </is>
       </c>
-      <c r="D10" s="301" t="n">
+      <c r="D10" s="311" t="n">
         <v>400</v>
       </c>
-      <c r="E10" s="301">
+      <c r="E10" s="311">
         <f>3+11</f>
         <v/>
       </c>
-      <c r="F10" s="301" t="n">
+      <c r="F10" s="311" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="301">
+      <c r="G10" s="311">
         <f>E10-F10</f>
         <v/>
       </c>
@@ -3031,33 +3031,33 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="301" t="inlineStr">
+      <c r="A11" s="311" t="inlineStr">
         <is>
           <t>Lt. SAPPHIRE</t>
         </is>
       </c>
-      <c r="B11" s="301" t="inlineStr">
+      <c r="B11" s="311" t="inlineStr">
         <is>
           <t>mix</t>
         </is>
       </c>
-      <c r="C11" s="301" t="inlineStr">
+      <c r="C11" s="311" t="inlineStr">
         <is>
           <t>1000-1200</t>
         </is>
       </c>
-      <c r="D11" s="301" t="n">
+      <c r="D11" s="311" t="n">
         <v>400</v>
       </c>
-      <c r="E11" s="301">
+      <c r="E11" s="311">
         <f>7+4</f>
         <v/>
       </c>
-      <c r="F11" s="301">
+      <c r="F11" s="311">
         <f>1+2</f>
         <v/>
       </c>
-      <c r="G11" s="301">
+      <c r="G11" s="311">
         <f>E11-F11</f>
         <v/>
       </c>
@@ -3073,29 +3073,29 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="301" t="inlineStr">
+      <c r="A12" s="311" t="inlineStr">
         <is>
           <t>Montana</t>
         </is>
       </c>
-      <c r="B12" s="301" t="inlineStr">
+      <c r="B12" s="311" t="inlineStr">
         <is>
           <t>mix</t>
         </is>
       </c>
-      <c r="C12" s="301" t="inlineStr">
+      <c r="C12" s="311" t="inlineStr">
         <is>
           <t>1000-1200</t>
         </is>
       </c>
-      <c r="D12" s="301" t="n">
+      <c r="D12" s="311" t="n">
         <v>400</v>
       </c>
-      <c r="E12" s="301" t="n">
+      <c r="E12" s="311" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="301" t="n"/>
-      <c r="G12" s="301">
+      <c r="F12" s="311" t="n"/>
+      <c r="G12" s="311">
         <f>E12-F12</f>
         <v/>
       </c>
@@ -3111,32 +3111,32 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="301" t="inlineStr">
+      <c r="A13" s="311" t="inlineStr">
         <is>
           <t>AQUAMARINE</t>
         </is>
       </c>
-      <c r="B13" s="301" t="inlineStr">
+      <c r="B13" s="311" t="inlineStr">
         <is>
           <t>mix</t>
         </is>
       </c>
-      <c r="C13" s="301" t="inlineStr">
+      <c r="C13" s="311" t="inlineStr">
         <is>
           <t>1000-1200</t>
         </is>
       </c>
-      <c r="D13" s="301" t="n">
+      <c r="D13" s="311" t="n">
         <v>400</v>
       </c>
-      <c r="E13" s="301" t="n">
+      <c r="E13" s="311" t="n">
         <v>10</v>
       </c>
-      <c r="F13" s="301">
+      <c r="F13" s="311">
         <f>2+1</f>
         <v/>
       </c>
-      <c r="G13" s="301">
+      <c r="G13" s="311">
         <f>E13-F13</f>
         <v/>
       </c>
@@ -3157,26 +3157,26 @@
           <t>Tanzanite</t>
         </is>
       </c>
-      <c r="B14" s="312" t="inlineStr">
+      <c r="B14" s="314" t="inlineStr">
         <is>
           <t>mix</t>
         </is>
       </c>
-      <c r="C14" s="312" t="inlineStr">
+      <c r="C14" s="314" t="inlineStr">
         <is>
           <t>1000-1200</t>
         </is>
       </c>
-      <c r="D14" s="301" t="n">
+      <c r="D14" s="311" t="n">
         <v>400</v>
       </c>
-      <c r="E14" s="301" t="n">
+      <c r="E14" s="311" t="n">
         <v>8</v>
       </c>
-      <c r="F14" s="301" t="n">
+      <c r="F14" s="311" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="301">
+      <c r="G14" s="311">
         <f>E14-F14</f>
         <v/>
       </c>
@@ -3192,29 +3192,29 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="301" t="inlineStr">
+      <c r="A15" s="311" t="inlineStr">
         <is>
           <t>MOCHA YELLOW</t>
         </is>
       </c>
-      <c r="B15" s="301" t="inlineStr">
+      <c r="B15" s="311" t="inlineStr">
         <is>
           <t>mix</t>
         </is>
       </c>
-      <c r="C15" s="301" t="inlineStr">
+      <c r="C15" s="311" t="inlineStr">
         <is>
           <t>1000-1200</t>
         </is>
       </c>
-      <c r="D15" s="301" t="n">
+      <c r="D15" s="311" t="n">
         <v>600</v>
       </c>
-      <c r="E15" s="301" t="n">
+      <c r="E15" s="311" t="n">
         <v>6</v>
       </c>
-      <c r="F15" s="301" t="n"/>
-      <c r="G15" s="301">
+      <c r="F15" s="311" t="n"/>
+      <c r="G15" s="311">
         <f>E15-F15</f>
         <v/>
       </c>
@@ -3230,29 +3230,29 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="301" t="inlineStr">
+      <c r="A16" s="311" t="inlineStr">
         <is>
           <t>MOCHA  ROSE</t>
         </is>
       </c>
-      <c r="B16" s="301" t="inlineStr">
+      <c r="B16" s="311" t="inlineStr">
         <is>
           <t>mix</t>
         </is>
       </c>
-      <c r="C16" s="301" t="inlineStr">
+      <c r="C16" s="311" t="inlineStr">
         <is>
           <t>1000-1200</t>
         </is>
       </c>
-      <c r="D16" s="301" t="n">
+      <c r="D16" s="311" t="n">
         <v>600</v>
       </c>
-      <c r="E16" s="301" t="n">
+      <c r="E16" s="311" t="n">
         <v>5</v>
       </c>
-      <c r="F16" s="301" t="n"/>
-      <c r="G16" s="301">
+      <c r="F16" s="311" t="n"/>
+      <c r="G16" s="311">
         <f>E16-F16</f>
         <v/>
       </c>
@@ -3268,32 +3268,32 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="301" t="inlineStr">
+      <c r="A17" s="311" t="inlineStr">
         <is>
           <t>Lt. Rose</t>
         </is>
       </c>
-      <c r="B17" s="301" t="inlineStr">
+      <c r="B17" s="311" t="inlineStr">
         <is>
           <t>mix</t>
         </is>
       </c>
-      <c r="C17" s="301" t="inlineStr">
+      <c r="C17" s="311" t="inlineStr">
         <is>
           <t>1000-1200</t>
         </is>
       </c>
-      <c r="D17" s="301" t="n">
+      <c r="D17" s="311" t="n">
         <v>900</v>
       </c>
-      <c r="E17" s="301">
+      <c r="E17" s="311">
         <f>5+5+3</f>
         <v/>
       </c>
-      <c r="F17" s="301" t="n">
+      <c r="F17" s="311" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="301">
+      <c r="G17" s="311">
         <f>E17-F17</f>
         <v/>
       </c>
@@ -3309,31 +3309,31 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="301" t="inlineStr">
+      <c r="A18" s="311" t="inlineStr">
         <is>
           <t>Lt. Peach</t>
         </is>
       </c>
-      <c r="B18" s="301" t="inlineStr">
+      <c r="B18" s="311" t="inlineStr">
         <is>
           <t>mix</t>
         </is>
       </c>
-      <c r="C18" s="301" t="inlineStr">
+      <c r="C18" s="311" t="inlineStr">
         <is>
           <t>1000-1200</t>
         </is>
       </c>
-      <c r="D18" s="301" t="n">
+      <c r="D18" s="311" t="n">
         <v>500</v>
       </c>
-      <c r="E18" s="301" t="n">
+      <c r="E18" s="311" t="n">
         <v>11</v>
       </c>
-      <c r="F18" s="301" t="n">
+      <c r="F18" s="311" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="301">
+      <c r="G18" s="311">
         <f>E18-F18</f>
         <v/>
       </c>
@@ -3349,31 +3349,31 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="301" t="inlineStr">
+      <c r="A19" s="311" t="inlineStr">
         <is>
           <t>GOLD SHADOW</t>
         </is>
       </c>
-      <c r="B19" s="301" t="inlineStr">
+      <c r="B19" s="311" t="inlineStr">
         <is>
           <t>mix</t>
         </is>
       </c>
-      <c r="C19" s="301" t="inlineStr">
+      <c r="C19" s="311" t="inlineStr">
         <is>
           <t>1000-1200</t>
         </is>
       </c>
-      <c r="D19" s="301" t="n">
+      <c r="D19" s="311" t="n">
         <v>400</v>
       </c>
-      <c r="E19" s="301" t="n">
+      <c r="E19" s="311" t="n">
         <v>4</v>
       </c>
-      <c r="F19" s="301" t="n">
+      <c r="F19" s="311" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="301">
+      <c r="G19" s="311">
         <f>E19-F19</f>
         <v/>
       </c>
@@ -3389,32 +3389,32 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="301" t="inlineStr">
+      <c r="A20" s="311" t="inlineStr">
         <is>
           <t>AMETHYST</t>
         </is>
       </c>
-      <c r="B20" s="301" t="inlineStr">
+      <c r="B20" s="311" t="inlineStr">
         <is>
           <t>mix</t>
         </is>
       </c>
-      <c r="C20" s="301" t="inlineStr">
+      <c r="C20" s="311" t="inlineStr">
         <is>
           <t>1000-1200</t>
         </is>
       </c>
-      <c r="D20" s="301" t="n">
+      <c r="D20" s="311" t="n">
         <v>400</v>
       </c>
-      <c r="E20" s="301" t="n">
+      <c r="E20" s="311" t="n">
         <v>9</v>
       </c>
-      <c r="F20" s="301">
+      <c r="F20" s="311">
         <f>1+1+2</f>
         <v/>
       </c>
-      <c r="G20" s="301">
+      <c r="G20" s="311">
         <f>E20-F20</f>
         <v/>
       </c>
@@ -3430,29 +3430,29 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="301" t="inlineStr">
+      <c r="A21" s="311" t="inlineStr">
         <is>
           <t>Lt. Colorado Topaz</t>
         </is>
       </c>
-      <c r="B21" s="301" t="inlineStr">
+      <c r="B21" s="311" t="inlineStr">
         <is>
           <t>mix</t>
         </is>
       </c>
-      <c r="C21" s="301" t="inlineStr">
+      <c r="C21" s="311" t="inlineStr">
         <is>
           <t>1000-1200</t>
         </is>
       </c>
-      <c r="D21" s="301" t="n">
+      <c r="D21" s="311" t="n">
         <v>400</v>
       </c>
-      <c r="E21" s="301" t="n">
+      <c r="E21" s="311" t="n">
         <v>5</v>
       </c>
-      <c r="F21" s="301" t="n"/>
-      <c r="G21" s="301">
+      <c r="F21" s="311" t="n"/>
+      <c r="G21" s="311">
         <f>E21-F21</f>
         <v/>
       </c>
@@ -3468,29 +3468,29 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="301" t="inlineStr">
+      <c r="A22" s="311" t="inlineStr">
         <is>
           <t>BLUE MOONLIGHT</t>
         </is>
       </c>
-      <c r="B22" s="301" t="inlineStr">
+      <c r="B22" s="311" t="inlineStr">
         <is>
           <t>mix</t>
         </is>
       </c>
-      <c r="C22" s="301" t="inlineStr">
+      <c r="C22" s="311" t="inlineStr">
         <is>
           <t>1000-1200</t>
         </is>
       </c>
-      <c r="D22" s="301" t="n">
+      <c r="D22" s="311" t="n">
         <v>500</v>
       </c>
-      <c r="E22" s="301" t="n">
+      <c r="E22" s="311" t="n">
         <v>6</v>
       </c>
-      <c r="F22" s="301" t="n"/>
-      <c r="G22" s="301">
+      <c r="F22" s="311" t="n"/>
+      <c r="G22" s="311">
         <f>E22-F22</f>
         <v/>
       </c>
@@ -3506,30 +3506,30 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="301" t="inlineStr">
+      <c r="A23" s="311" t="inlineStr">
         <is>
           <t>TOPAZ</t>
         </is>
       </c>
-      <c r="B23" s="301" t="inlineStr">
+      <c r="B23" s="311" t="inlineStr">
         <is>
           <t>mix</t>
         </is>
       </c>
-      <c r="C23" s="301" t="inlineStr">
+      <c r="C23" s="311" t="inlineStr">
         <is>
           <t>1000-1200</t>
         </is>
       </c>
-      <c r="D23" s="301" t="n">
+      <c r="D23" s="311" t="n">
         <v>400</v>
       </c>
-      <c r="E23" s="301">
+      <c r="E23" s="311">
         <f>3+6+7</f>
         <v/>
       </c>
-      <c r="F23" s="301" t="n"/>
-      <c r="G23" s="301">
+      <c r="F23" s="311" t="n"/>
+      <c r="G23" s="311">
         <f>E23-F23</f>
         <v/>
       </c>
@@ -3545,31 +3545,31 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="301" t="inlineStr">
+      <c r="A24" s="311" t="inlineStr">
         <is>
           <t>SMOKED TOPAZ</t>
         </is>
       </c>
-      <c r="B24" s="301" t="inlineStr">
+      <c r="B24" s="311" t="inlineStr">
         <is>
           <t>mix</t>
         </is>
       </c>
-      <c r="C24" s="301" t="inlineStr">
+      <c r="C24" s="311" t="inlineStr">
         <is>
           <t>1000-1200</t>
         </is>
       </c>
-      <c r="D24" s="301" t="n">
+      <c r="D24" s="311" t="n">
         <v>400</v>
       </c>
-      <c r="E24" s="301" t="n">
+      <c r="E24" s="311" t="n">
         <v>19</v>
       </c>
-      <c r="F24" s="301" t="n">
+      <c r="F24" s="311" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="301">
+      <c r="G24" s="311">
         <f>E24-F24</f>
         <v/>
       </c>
@@ -3585,31 +3585,31 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="301" t="inlineStr">
+      <c r="A25" s="311" t="inlineStr">
         <is>
           <t>Black Diamond</t>
         </is>
       </c>
-      <c r="B25" s="301" t="inlineStr">
+      <c r="B25" s="311" t="inlineStr">
         <is>
           <t>mix</t>
         </is>
       </c>
-      <c r="C25" s="301" t="inlineStr">
+      <c r="C25" s="311" t="inlineStr">
         <is>
           <t>1000-1200</t>
         </is>
       </c>
-      <c r="D25" s="301" t="n">
+      <c r="D25" s="311" t="n">
         <v>500</v>
       </c>
-      <c r="E25" s="301" t="n">
+      <c r="E25" s="311" t="n">
         <v>5</v>
       </c>
-      <c r="F25" s="301" t="n">
+      <c r="F25" s="311" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="301">
+      <c r="G25" s="311">
         <f>E25-F25</f>
         <v/>
       </c>
@@ -3625,33 +3625,33 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="301" t="inlineStr">
+      <c r="A26" s="311" t="inlineStr">
         <is>
           <t>EMERALD</t>
         </is>
       </c>
-      <c r="B26" s="301" t="inlineStr">
+      <c r="B26" s="311" t="inlineStr">
         <is>
           <t>mix</t>
         </is>
       </c>
-      <c r="C26" s="301" t="inlineStr">
+      <c r="C26" s="311" t="inlineStr">
         <is>
           <t>1000-1200</t>
         </is>
       </c>
-      <c r="D26" s="301" t="n">
+      <c r="D26" s="311" t="n">
         <v>400</v>
       </c>
-      <c r="E26" s="301">
+      <c r="E26" s="311">
         <f>1+4+15</f>
         <v/>
       </c>
-      <c r="F26" s="301">
+      <c r="F26" s="311">
         <f>1+1</f>
         <v/>
       </c>
-      <c r="G26" s="301">
+      <c r="G26" s="311">
         <f>E26-F26</f>
         <v/>
       </c>
@@ -3667,32 +3667,32 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="301" t="inlineStr">
+      <c r="A27" s="311" t="inlineStr">
         <is>
           <t>CRYSTAL</t>
         </is>
       </c>
-      <c r="B27" s="301" t="inlineStr">
+      <c r="B27" s="311" t="inlineStr">
         <is>
           <t>mix</t>
         </is>
       </c>
-      <c r="C27" s="301" t="inlineStr">
+      <c r="C27" s="311" t="inlineStr">
         <is>
           <t>1000-1200</t>
         </is>
       </c>
-      <c r="D27" s="301" t="n">
+      <c r="D27" s="311" t="n">
         <v>300</v>
       </c>
-      <c r="E27" s="301" t="n">
+      <c r="E27" s="311" t="n">
         <v>13</v>
       </c>
-      <c r="F27" s="301">
+      <c r="F27" s="311">
         <f>1+1+1+1</f>
         <v/>
       </c>
-      <c r="G27" s="301">
+      <c r="G27" s="311">
         <f>E27-F27</f>
         <v/>
       </c>
@@ -3713,25 +3713,25 @@
           <t>Seffaf</t>
         </is>
       </c>
-      <c r="B28" s="312" t="inlineStr">
+      <c r="B28" s="314" t="inlineStr">
         <is>
           <t>mix</t>
         </is>
       </c>
-      <c r="C28" s="312" t="inlineStr">
+      <c r="C28" s="314" t="inlineStr">
         <is>
           <t>1000-1200</t>
         </is>
       </c>
-      <c r="D28" s="301" t="n">
+      <c r="D28" s="311" t="n">
         <v>300</v>
       </c>
-      <c r="E28" s="301">
+      <c r="E28" s="311">
         <f>40+3</f>
         <v/>
       </c>
-      <c r="F28" s="301" t="n"/>
-      <c r="G28" s="301">
+      <c r="F28" s="311" t="n"/>
+      <c r="G28" s="311">
         <f>E28-F28</f>
         <v/>
       </c>
@@ -3747,30 +3747,30 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="301" t="inlineStr">
+      <c r="A29" s="311" t="inlineStr">
         <is>
           <t>ROSE</t>
         </is>
       </c>
-      <c r="B29" s="301" t="inlineStr">
+      <c r="B29" s="311" t="inlineStr">
         <is>
           <t>mix</t>
         </is>
       </c>
-      <c r="C29" s="301" t="inlineStr">
+      <c r="C29" s="311" t="inlineStr">
         <is>
           <t>1000-1200</t>
         </is>
       </c>
-      <c r="D29" s="301" t="n">
+      <c r="D29" s="311" t="n">
         <v>900</v>
       </c>
-      <c r="E29" s="301">
+      <c r="E29" s="311">
         <f>9+6</f>
         <v/>
       </c>
-      <c r="F29" s="301" t="n"/>
-      <c r="G29" s="301">
+      <c r="F29" s="311" t="n"/>
+      <c r="G29" s="311">
         <f>E29-F29</f>
         <v/>
       </c>
@@ -3786,32 +3786,32 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="301" t="inlineStr">
+      <c r="A30" s="311" t="inlineStr">
         <is>
           <t>Citrine</t>
         </is>
       </c>
-      <c r="B30" s="301" t="inlineStr">
+      <c r="B30" s="311" t="inlineStr">
         <is>
           <t>mix</t>
         </is>
       </c>
-      <c r="C30" s="301" t="inlineStr">
+      <c r="C30" s="311" t="inlineStr">
         <is>
           <t>1000-1200</t>
         </is>
       </c>
-      <c r="D30" s="301" t="n">
+      <c r="D30" s="311" t="n">
         <v>500</v>
       </c>
-      <c r="E30" s="301">
+      <c r="E30" s="311">
         <f>7+8</f>
         <v/>
       </c>
-      <c r="F30" s="301" t="n">
+      <c r="F30" s="311" t="n">
         <v>3</v>
       </c>
-      <c r="G30" s="301">
+      <c r="G30" s="311">
         <f>E30-F30</f>
         <v/>
       </c>
@@ -3827,35 +3827,35 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="301" t="inlineStr">
+      <c r="A31" s="311" t="inlineStr">
         <is>
           <t xml:space="preserve">Crystal AB </t>
         </is>
       </c>
-      <c r="B31" s="301" t="inlineStr">
+      <c r="B31" s="311" t="inlineStr">
         <is>
           <t>mix</t>
         </is>
       </c>
-      <c r="C31" s="301" t="inlineStr">
+      <c r="C31" s="311" t="inlineStr">
         <is>
           <t>1000-1200</t>
         </is>
       </c>
-      <c r="D31" s="301" t="n">
+      <c r="D31" s="311" t="n">
         <v>300</v>
       </c>
-      <c r="E31" s="301" t="n">
+      <c r="E31" s="311" t="n">
         <v>7</v>
       </c>
-      <c r="F31" s="301" t="n">
+      <c r="F31" s="311" t="n">
         <v>1</v>
       </c>
-      <c r="G31" s="301">
+      <c r="G31" s="311">
         <f>E31-F31</f>
         <v/>
       </c>
-      <c r="H31" s="301" t="inlineStr">
+      <c r="H31" s="311" t="inlineStr">
         <is>
           <t>001+</t>
         </is>
